--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -444,12 +444,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
     </row>
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D5" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="D7" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9">
@@ -589,7 +589,7 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>486</v>
+        <v>413</v>
       </c>
       <c r="D16" t="n">
-        <v>413</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>65</v>
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="D20" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>362</v>
+        <v>219</v>
       </c>
       <c r="D21" t="n">
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1050</v>
+        <v>857</v>
       </c>
       <c r="D23" t="n">
-        <v>857</v>
+        <v>846</v>
       </c>
     </row>
   </sheetData>
@@ -802,12 +802,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
     </row>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
         <v>4</v>
-      </c>
-      <c r="D13" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>65</v>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
     </row>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D2" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
         <v>23</v>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D6" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1320,7 +1320,7 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>22</v>
+      </c>
+      <c r="D8" t="n">
         <v>13</v>
-      </c>
-      <c r="D8" t="n">
-        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
         <v>5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
     </row>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -1567,7 +1567,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="D18" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1904,7 +1904,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1937,7 +1937,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
     </row>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -2223,7 +2223,7 @@
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -2292,10 +2292,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
         <v>6</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D11" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2356,12 +2356,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
     </row>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -2784,7 +2784,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -2838,7 +2838,7 @@
         <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2935,12 +2935,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
@@ -2992,10 +2992,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -3092,12 +3092,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
     </row>
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D5" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -3195,12 +3195,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
     </row>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -3234,10 +3234,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="D9" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3492,7 +3492,7 @@
         <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3506,7 +3506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>23/08</t>
+          <t>30/08</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
     </row>
@@ -3543,185 +3543,167 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Adabraka</t>
+          <t>Arena</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Emmanuel Otiboe</t>
+          <t>Zephaniah Lartey</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Arena</t>
+          <t>ATU Church</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zephaniah Lartey</t>
+          <t>James Pekyie</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ATU Church</t>
+          <t>ATU Main Campus</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>James Pekyie</t>
+          <t>Racheal Boamah</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ATU Main Campus</t>
+          <t>City Campus</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Racheal Boamah</t>
+          <t>Abednego Abbey</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>City Campus</t>
+          <t>Jamestown</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Abednego Abbey</t>
+          <t>Joel Quartey</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jamestown</t>
+          <t>Jamestown Allos</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Joel Quartey</t>
+          <t>Ishmael Oplerm</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jamestown Allos</t>
+          <t>UssherFort</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ishmael Oplerm</t>
+          <t>Seth Kpelebe</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UssherFort</t>
+          <t>Yours and Ours</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Seth Kpelebe</t>
+          <t>Prince Odum</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yours and Ours</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Prince Odum</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>154</v>
-      </c>
-      <c r="D12" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -444,12 +444,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
     </row>
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D3" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D6" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D7" t="n">
-        <v>220</v>
+        <v>258</v>
       </c>
     </row>
     <row r="9">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>110</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13">
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D13" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16">
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="D16" t="n">
-        <v>396</v>
+        <v>522</v>
       </c>
     </row>
     <row r="18">
@@ -710,7 +710,7 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D19" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D20" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="D21" t="n">
-        <v>230</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>857</v>
+        <v>846</v>
       </c>
       <c r="D23" t="n">
-        <v>846</v>
+        <v>991</v>
       </c>
     </row>
   </sheetData>
@@ -802,12 +802,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
         <v>8</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1055,7 +1055,7 @@
         <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
     </row>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -1163,7 +1163,7 @@
         <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D6" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
     </row>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -1317,10 +1317,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -1425,10 +1425,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D14" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
     </row>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D4" t="n">
         <v>12</v>
-      </c>
-      <c r="D4" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -1564,10 +1564,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
         <v>3</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
         <v>5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -1639,7 +1639,7 @@
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1672,10 +1672,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D18" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -1994,7 +1994,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2145,12 +2145,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
     </row>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -2220,10 +2220,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -2292,7 +2292,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D11" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2356,12 +2356,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2398,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -2431,10 +2431,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -2470,7 +2470,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
         <v>7</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -2524,7 +2524,7 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -2542,7 +2542,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
     </row>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2642,10 +2642,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -2663,7 +2663,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2706,12 +2706,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
     </row>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -2781,10 +2781,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9">
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -2871,10 +2871,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -2892,7 +2892,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2935,12 +2935,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -2992,10 +2992,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -3092,12 +3092,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
     </row>
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -3131,10 +3131,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -3195,12 +3195,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
     </row>
@@ -3216,10 +3216,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
         <v>15</v>
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
         <v>11</v>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3419,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
     </row>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3506,7 +3506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3522,12 +3522,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>30/08</t>
+          <t>06/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
     </row>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -3564,7 +3564,7 @@
         <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
         <v>18</v>
@@ -3669,41 +3669,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Yours and Ours</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Prince Odum</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>120</v>
-      </c>
-      <c r="D11" t="n">
-        <v>110</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -444,12 +444,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
     </row>
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -483,10 +483,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D3" t="n">
-        <v>67</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D5" t="n">
-        <v>51</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6">
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D6" t="n">
-        <v>77</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="D7" t="n">
-        <v>258</v>
+        <v>545</v>
       </c>
     </row>
     <row r="9">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12">
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>106</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>73</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>98</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16">
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>396</v>
+        <v>517</v>
       </c>
       <c r="D16" t="n">
-        <v>522</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="18">
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D18" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D19" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D20" t="n">
-        <v>63</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
@@ -756,10 +756,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="D21" t="n">
-        <v>211</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>846</v>
+        <v>986</v>
       </c>
       <c r="D23" t="n">
-        <v>991</v>
+        <v>1674</v>
       </c>
     </row>
   </sheetData>
@@ -802,12 +802,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
     </row>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1003,10 +1003,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
     </row>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D2" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -1160,10 +1160,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D5" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="D6" t="n">
-        <v>106</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
     </row>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -1308,52 +1308,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GTUC</t>
+          <t>GTUC Allos</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Richard Manu</t>
+          <t>Michael Oteng</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GTUC Allos</t>
+          <t>GTUC Allos 3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Michael Oteng</t>
+          <t>Sylvester Ntumy</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GTUC Allos 3</t>
+          <t>GTUC Main Campus</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sylvester Ntumy</t>
+          <t>Jeremiah Ashong</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1362,86 +1362,68 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GTUC Main Campus</t>
+          <t>Kings University</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jeremiah Ashong</t>
+          <t>Samuel Tigah</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kings University</t>
+          <t>Korle Bu Light</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Samuel Tigah</t>
+          <t>Sonia Elolo</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Korle Bu Light</t>
+          <t>Regent University</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sonia Elolo</t>
+          <t>Prince Forson</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Regent University</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Prince Forson</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>104</v>
-      </c>
-      <c r="D14" t="n">
-        <v>101</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -1455,7 +1437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1471,12 +1453,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
     </row>
@@ -1492,10 +1474,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1510,10 +1492,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1528,10 +1510,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1555,230 +1537,212 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Block A Beta</t>
+          <t>Block B Annex New</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gracy Wellington</t>
+          <t>Kevin Brown</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Block B Annex New</t>
+          <t>Commonwealth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kevin Brown</t>
+          <t>Peter Tefuttor</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Commonwealth</t>
+          <t>Diamond Jubilee New</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Peter Tefuttor</t>
+          <t>Emelda Antwi-Agyei</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Diamond Jubilee New</t>
+          <t>Evandy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Emelda Antwi-Agyei</t>
+          <t>Delali Apedu</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Evandy</t>
+          <t>Evandy Annex New</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Delali Apedu</t>
+          <t>Caroline Hammond</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Evandy Annex New</t>
+          <t>Pent B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Caroline Hammond</t>
+          <t>Yves Mensah</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pent B</t>
+          <t>Pent C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Yves Mensah</t>
+          <t>Roland Cudjoe</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pent C</t>
+          <t>Pent Old &amp; A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Roland Cudjoe</t>
+          <t>Nana Kofi Danso-Mensah</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pent Old &amp; A</t>
+          <t>TF Annex New</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Samuel Boateng</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TF Annex New</t>
+          <t>Vacation Church</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Samuel Boateng</t>
+          <t>Antoinette Annan</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Volta</t>
+          <t>Volta Annex New</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stephanie Seglah</t>
+          <t>Esllah Osei</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Volta Annex New</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Esllah Osei</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>104</v>
-      </c>
-      <c r="D18" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1808,12 +1772,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
     </row>
@@ -1829,10 +1793,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1847,10 +1811,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1883,10 +1847,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -1901,7 +1865,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1919,7 +1883,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1955,10 +1919,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -1991,10 +1955,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -2027,10 +1991,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -2045,10 +2009,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -2081,7 +2045,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -2112,10 +2076,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D18" t="n">
-        <v>63</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2145,12 +2109,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
     </row>
@@ -2166,10 +2130,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -2202,10 +2166,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -2220,10 +2184,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -2238,10 +2202,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -2256,10 +2220,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -2274,10 +2238,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -2295,7 +2259,7 @@
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -2310,10 +2274,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -2323,10 +2287,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D11" t="n">
-        <v>73</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2356,12 +2320,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2341,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -2395,10 +2359,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -2413,10 +2377,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -2431,10 +2395,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -2449,10 +2413,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -2467,10 +2431,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -2488,7 +2452,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -2503,10 +2467,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -2521,10 +2485,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -2539,10 +2503,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -2557,10 +2521,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -2570,10 +2534,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -2603,12 +2567,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
     </row>
@@ -2624,10 +2588,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -2642,10 +2606,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -2660,10 +2624,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -2673,10 +2637,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2706,12 +2670,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
     </row>
@@ -2745,10 +2709,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -2781,10 +2745,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -2799,10 +2763,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -2835,10 +2799,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -2853,10 +2817,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -2871,10 +2835,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
@@ -2889,7 +2853,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>4</v>
@@ -2902,10 +2866,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D12" t="n">
-        <v>67</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -2919,7 +2883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2935,12 +2899,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
     </row>
@@ -2956,10 +2920,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -2977,92 +2941,56 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Haatso Executive</t>
+          <t>Haatso West</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stephen Mensah</t>
+          <t>Michael Sarpong</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Haatso Melcom</t>
+          <t>THS Westland</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kenneth Koomson</t>
+          <t>Joseph Halivor</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Haatso West</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Michael Sarpong</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>THS Westland</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Joseph Halivor</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>32</v>
-      </c>
-      <c r="D8" t="n">
-        <v>37</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -3092,12 +3020,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
     </row>
@@ -3113,10 +3041,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -3131,10 +3059,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D3" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
@@ -3149,10 +3077,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -3162,10 +3090,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D5" t="n">
-        <v>51</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -3195,12 +3123,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
     </row>
@@ -3216,10 +3144,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -3237,7 +3165,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -3252,10 +3180,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -3270,10 +3198,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -3288,10 +3216,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -3306,10 +3234,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -3327,7 +3255,7 @@
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -3337,10 +3265,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D9" t="n">
-        <v>77</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -3370,12 +3298,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
     </row>
@@ -3419,12 +3347,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3389,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -3476,10 +3404,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -3489,10 +3417,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -3506,7 +3434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3522,12 +3450,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>06/09</t>
+          <t>13/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
     </row>
@@ -3543,10 +3471,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -3561,10 +3489,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4">
@@ -3579,10 +3507,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
@@ -3597,95 +3525,113 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>City Campus</t>
+          <t>ATU YWCA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Abednego Abbey</t>
+          <t>Emmanuel Otiboe</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jamestown</t>
+          <t>City Campus</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Joel Quartey</t>
+          <t>Abednego Abbey</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jamestown Allos</t>
+          <t>Jamestown</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ishmael Oplerm</t>
+          <t>Joel Quartey</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UssherFort</t>
+          <t>Jamestown Allos</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Seth Kpelebe</t>
+          <t>Ishmael Oplerm</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>UssherFort</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Seth Kpelebe</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>16</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>110</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="C11" t="n">
         <v>138</v>
+      </c>
+      <c r="D11" t="n">
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -13,16 +13,15 @@
     <sheet name="Colossians 3" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Colossians 4" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Colossians 5" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Galatians 1" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Galatians 10" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Galatians 2" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Galatians 3" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Galatians 4" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Galatians 5" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Galatians 6 A" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Galatians 7" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Galatians 8" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Galatians 9" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Galatians 10" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Galatians 2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Galatians 3" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Galatians 4" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Galatians 5" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Galatians 6 A" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Galatians 7" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Galatians 8" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Galatians 9" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,12 +443,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
     </row>
@@ -465,10 +464,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -483,10 +482,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="D3" t="n">
-        <v>156</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
@@ -501,10 +500,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="D4" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -519,10 +518,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="D5" t="n">
-        <v>143</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -537,10 +536,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="D6" t="n">
-        <v>136</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -550,229 +549,211 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>258</v>
+        <v>548</v>
       </c>
       <c r="D7" t="n">
-        <v>545</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Galatians 1</t>
+          <t>Galatians 10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Isaac Agyeman</t>
+          <t>Nii Nkunim Armar</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Galatians 10</t>
+          <t>Galatians 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Nii Nkunim Armar</t>
+          <t>Richmond Annan</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>329</v>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Galatians 2</t>
+          <t>Galatians 4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Richmond Annan</t>
+          <t>Eric Boachie Yiadom</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>329</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Galatians 4</t>
+          <t>Galatians 5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Eric Boachie Yiadom</t>
+          <t>Michael Oteng</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>106</v>
+        <v>168</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Galatians 5</t>
+          <t>Galatians 8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Michael Oteng</t>
+          <t>Caleb Osei-Kofi</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="D13" t="n">
-        <v>157</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Galatians 8</t>
+          <t>Galatians 9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Caleb Osei-Kofi</t>
+          <t>Divine Olubakinde</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>73</v>
+        <v>331</v>
       </c>
       <c r="D14" t="n">
-        <v>135</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Galatians 9</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Divine Olubakinde</t>
+          <t>Galatians Total</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>98</v>
+        <v>1149</v>
       </c>
       <c r="D15" t="n">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Galatians Total</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>517</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1016</v>
+        <v>393</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Galatians 3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Joseph Teye</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>27</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Galatians 3</t>
+          <t>Galatians 6 A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Joseph Teye</t>
+          <t>Nana Kofi Danso-Mensah</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Galatians 6 A</t>
+          <t>Galatians 7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Albert Gillies Heward-Mills</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Galatians 7</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Albert Gillies Heward-Mills</t>
+          <t>Jesus Night Total</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="D20" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Jesus Night Total</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>211</v>
-      </c>
-      <c r="D21" t="n">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>986</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1674</v>
+      <c r="C22" t="n">
+        <v>1810</v>
+      </c>
+      <c r="D22" t="n">
+        <v>633</v>
       </c>
     </row>
   </sheetData>
@@ -786,7 +767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,42 +783,42 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Campus Anagkazo</t>
+          <t>UPSA Campus Hostels</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nayram Gblorkpor</t>
+          <t>Andrew Heward-Mills</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Commonwealth 2 New</t>
+          <t>Upsa Diaspora</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>David Arhin</t>
+          <t>Bright Nurtey Tettey Tetteh</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -850,212 +831,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 1</t>
+          <t>UPSA Green Hostel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deborah Wiredu</t>
+          <t>Desmond Hlorgbey</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Limann</t>
+          <t>UPSA Hostels A &amp; B</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kwesi Boadu-Amoama</t>
+          <t>Jayson Quarshie</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Main Campus Dunamis</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Nana Kwame Barima</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>152</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Main Campus Proskuneo</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Isaac Baidoo</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Mensah Sarbah Poimen</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Prince Okai</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Prince of Peace New</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Joseph Akyem</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>8</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Revelations</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Edna Adorshie</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sarbah</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Joseph Teye</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>11</v>
-      </c>
-      <c r="D11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sey</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dennis Kpogli</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>9</v>
-      </c>
-      <c r="D12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sey New</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Frank Anokye</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Shemen</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Samuel Agyei</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>62</v>
-      </c>
-      <c r="D15" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1085,98 +904,224 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UPSA Campus Hostels</t>
+          <t>AIT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Andrew Heward-Mills</t>
+          <t>Lawrence Adetunji</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Upsa Diaspora</t>
+          <t>AIT Yeshua</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bright Nurtey Tettey Tetteh</t>
+          <t>Jonathan Ekhagbai</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UPSA Green Hostel</t>
+          <t>Aparche</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Desmond Hlorgbey</t>
+          <t>Cyrus-Dag Stephens</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UPSA Hostels A &amp; B</t>
+          <t>Galilea</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jayson Quarshie</t>
+          <t>Lady Vanessa Osei</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>GCTU Koinonia Governorship</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Christabel Tukpeyi</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GTUC Allos</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Michael Oteng</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>15</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GTUC Allos 3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sylvester Ntumy</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GTUC Main Campus</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jeremiah Ashong</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kings University</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Samuel Tigah</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Korle Bu Light</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sonia Elolo</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Regent University</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Prince Forson</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>41</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>106</v>
-      </c>
-      <c r="D6" t="n">
-        <v>149</v>
+      <c r="C13" t="n">
+        <v>168</v>
+      </c>
+      <c r="D13" t="n">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1206,64 +1151,64 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AIT</t>
+          <t>Akuafo New</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lawrence Adetunji</t>
+          <t>Karyn Tagoe</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AIT Yeshua</t>
+          <t>Area 1 Royals</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jonathan Ekhagbai</t>
+          <t>Kwame Darteh</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aparche</t>
+          <t>Bani</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cyrus-Dag Stephens</t>
+          <t>Kojo Afriyie</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1272,34 +1217,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Galilea</t>
+          <t>Block A Annex</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lady Vanessa Osei</t>
+          <t>Marcia Adomako</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCTU Koinonia Governorship</t>
+          <t>Block B Annex New</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Christabel Tukpeyi</t>
+          <t>Kevin Brown</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1308,66 +1253,66 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GTUC Allos</t>
+          <t>Commonwealth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Michael Oteng</t>
+          <t>Peter Tefuttor</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GTUC Allos 3</t>
+          <t>Diamond Jubilee New</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sylvester Ntumy</t>
+          <t>Emelda Antwi-Agyei</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GTUC Main Campus</t>
+          <t>Evandy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jeremiah Ashong</t>
+          <t>Delali Apedu</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kings University</t>
+          <t>Evandy Annex New</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Samuel Tigah</t>
+          <t>Caroline Hammond</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1380,50 +1325,122 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Korle Bu Light</t>
+          <t>Pent B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sonia Elolo</t>
+          <t>Yves Mensah</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Regent University</t>
+          <t>Pent C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prince Forson</t>
+          <t>Roland Cudjoe</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Pent Old &amp; A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nana Kofi Danso-Mensah</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TF Annex New</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Samuel Boateng</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Vacation Church</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Antoinette Annan</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Volta Annex New</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Esllah Osei</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>96</v>
-      </c>
-      <c r="D13" t="n">
-        <v>157</v>
+      <c r="C17" t="n">
+        <v>60</v>
+      </c>
+      <c r="D17" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1437,7 +1454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1453,28 +1470,28 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Akuafo New</t>
+          <t>Akuafo Charis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Karyn Tagoe</t>
+          <t>Stephen Asare Osei</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1483,52 +1500,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Area 1 Royals</t>
+          <t>Akuafo Hall 1 New</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kwame Darteh</t>
+          <t>Fredrick Anokye</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bani</t>
+          <t>Akuafo Hall 2 New</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kojo Afriyie</t>
+          <t>Dacosta Amponsah</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Block A Annex</t>
+          <t>Area 1  Logos</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marcia Adomako</t>
+          <t>Erasmus Laryea</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -1537,52 +1554,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Block B Annex New</t>
+          <t>Commonwealth 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kevin Brown</t>
+          <t>Lois Osei</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Commonwealth</t>
+          <t>Diamond Jubilee 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Peter Tefuttor</t>
+          <t>Abena Kyeremaa</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Diamond Jubilee New</t>
+          <t>Jesus Night TF New</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Emelda Antwi-Agyei</t>
+          <t>Jochebed Lawson-Heymann</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1591,30 +1608,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Evandy</t>
+          <t>Kwapong</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Delali Apedu</t>
+          <t>Eunice Owusu</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Evandy Annex New</t>
+          <t>Legon Hall</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Caroline Hammond</t>
+          <t>Edberg Ayensu</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1627,84 +1644,84 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pent B</t>
+          <t>Main Campus Allos</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yves Mensah</t>
+          <t>Albert Gillies Heward-Mills</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pent C</t>
+          <t>Main Campus Hagios</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Roland Cudjoe</t>
+          <t>Philmorra Laryea Okorley</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pent Old &amp; A</t>
+          <t>Main Campus Parakletos</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Melissa Meledi</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TF Annex New</t>
+          <t>Main Campus Pistis</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Samuel Boateng</t>
+          <t>Richard Mawuli Sogbo</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Vacation Church</t>
+          <t>Main Campus Tsalach</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Antoinette Annan</t>
+          <t>Jennifer Aidoo</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1717,32 +1734,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Volta Annex New</t>
+          <t>Main campus Zogreo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Esllah Osei</t>
+          <t>Elinam Fiagbe</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Volta Hall</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Precious Antwi</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>86</v>
-      </c>
-      <c r="D17" t="n">
-        <v>60</v>
+      <c r="C18" t="n">
+        <v>26</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1756,7 +1791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1772,46 +1807,46 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Akuafo Charis</t>
+          <t>AKUAFO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Stephen Asare Osei</t>
+          <t>Foanor Alloh</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Akuafo Hall 1 New</t>
+          <t>Akuafo Hall 6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fredrick Anokye</t>
+          <t>Ruby Nelson</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1820,70 +1855,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Akuafo Hall 2 New</t>
+          <t>Akuafo Zoe</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dacosta Amponsah</t>
+          <t>Enoch Bentil</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Area 1  Logos</t>
+          <t>ELU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Erasmus Laryea</t>
+          <t>Tracy Osei</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Commonwealth 1</t>
+          <t>Legon hall</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lois Osei</t>
+          <t>Nana Ahema Forson</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 2</t>
+          <t>Legon Hall B</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Abena Kyeremaa</t>
+          <t>Yosi Forson</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -1892,52 +1927,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jesus Night TF New</t>
+          <t>Volta</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Jochebed Lawson-Heymann</t>
+          <t>Caleb Osei-Kofi</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kwapong</t>
+          <t>Volta Mega</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Eunice Owusu</t>
+          <t>Doris Ainooh</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Legon Hall</t>
+          <t>Volta Others</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Edberg Ayensu</t>
+          <t>Rachael Sekyiwaaa</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -1946,140 +1981,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Main Campus Allos</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Albert Gillies Heward-Mills</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Main Campus Hagios</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Philmorra Laryea Okorley</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Main Campus Parakletos</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Melissa Meledi</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Main Campus Pistis</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Richard Mawuli Sogbo</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
         <v>20</v>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Main Campus Tsalach</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Jennifer Aidoo</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Main campus Zogreo</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Elinam Fiagbe</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Volta Hall</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Precious Antwi</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>63</v>
-      </c>
-      <c r="D18" t="n">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2093,217 +2002,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>13/09</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>20/09</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AKUAFO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Foanor Alloh</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>17</v>
-      </c>
-      <c r="D2" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Akuafo Hall 6</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ruby Nelson</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Akuafo Zoe</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Enoch Bentil</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>11</v>
-      </c>
-      <c r="D4" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ELU</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Tracy Osei</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Legon hall</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Nana Ahema Forson</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Legon Hall B</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Yosi Forson</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Volta</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Caleb Osei-Kofi</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>18</v>
-      </c>
-      <c r="D8" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Volta Mega</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Doris Ainooh</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>9</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Volta Others</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Rachael Sekyiwaaa</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>73</v>
-      </c>
-      <c r="D11" t="n">
-        <v>135</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2320,12 +2018,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
     </row>
@@ -2341,10 +2039,10 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>33</v>
+      </c>
+      <c r="D2" t="n">
         <v>11</v>
-      </c>
-      <c r="D2" t="n">
-        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -2359,10 +2057,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2377,10 +2075,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -2395,10 +2093,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2413,10 +2111,10 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>32</v>
+      </c>
+      <c r="D6" t="n">
         <v>10</v>
-      </c>
-      <c r="D6" t="n">
-        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -2431,10 +2129,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -2449,10 +2147,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -2467,10 +2165,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -2485,10 +2183,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -2503,10 +2201,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -2521,10 +2219,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -2534,10 +2232,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>331</v>
       </c>
       <c r="D13" t="n">
-        <v>224</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2567,12 +2265,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
     </row>
@@ -2588,10 +2286,10 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2" t="n">
         <v>9</v>
-      </c>
-      <c r="D2" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -2606,10 +2304,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2624,10 +2322,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2637,10 +2335,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2654,7 +2352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2670,12 +2368,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
     </row>
@@ -2709,167 +2407,131 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abundant Life West</t>
+          <t>Communication</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eshal Gabriel</t>
+          <t>Vicentia Boakye</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Communication</t>
+          <t>Deacon's Academy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vicentia Boakye</t>
+          <t>Gideon Boateng</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Deacon's Academy</t>
+          <t>Dome Main</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gideon Boateng</t>
+          <t>John Amoako</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dome Main</t>
+          <t>Dome Ministries</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>John Amoako</t>
+          <t>Wilhermina Teprey</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dome Ministries</t>
+          <t>Dome North</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wilhermina Teprey</t>
+          <t>Pearl Addo</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dome North</t>
+          <t>Kisseman</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pearl Addo</t>
+          <t>Victoria Affran</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kisseman</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Victoria Affran</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Taifa Burkina</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Samuel Brown</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>4</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>67</v>
-      </c>
-      <c r="D12" t="n">
-        <v>156</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2899,12 +2561,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
     </row>
@@ -2920,10 +2582,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -2938,10 +2600,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2956,10 +2618,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -2974,10 +2636,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -2987,10 +2649,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="D6" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -3020,12 +2682,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
     </row>
@@ -3041,10 +2703,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D2" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -3059,10 +2721,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -3077,10 +2739,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -3090,10 +2752,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="D5" t="n">
-        <v>143</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -3123,12 +2785,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
     </row>
@@ -3144,10 +2806,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -3162,10 +2824,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -3180,10 +2842,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -3198,10 +2860,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -3216,10 +2878,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3234,10 +2896,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -3252,10 +2914,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -3265,10 +2927,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="D9" t="n">
-        <v>136</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -3282,7 +2944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3298,26 +2960,80 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>ACM</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nii Nkunim Armar</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ACM 2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Daniel Orleans-Lindsay</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ACM 3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Joan Obakpolor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
+      <c r="C5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3331,7 +3047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3347,28 +3063,28 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>Accra City</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nii Nkunim Armar</t>
+          <t>Ferdinand Adams</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -3377,50 +3093,158 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACM 2</t>
+          <t>Arena</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Daniel Orleans-Lindsay</t>
+          <t>Zephaniah Lartey</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ACM 3</t>
+          <t>ATU Church</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Joan Obakpolor</t>
+          <t>James Pekyie</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>ATU Main Campus</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Racheal Boamah</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>31</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ATU YWCA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Emmanuel Otiboe</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>City Campus</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Abednego Abbey</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>40</v>
+      </c>
+      <c r="D7" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Jamestown</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Joel Quartey</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>33</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Jamestown Allos</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ishmael Oplerm</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>32</v>
+      </c>
+      <c r="D9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UssherFort</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Seth Kpelebe</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>30</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>22</v>
+      <c r="C11" t="n">
+        <v>329</v>
+      </c>
+      <c r="D11" t="n">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -3434,7 +3258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3450,188 +3274,260 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>13/09</t>
+          <t>20/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Accra City</t>
+          <t>Campus Anagkazo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ferdinand Adams</t>
+          <t>Nayram Gblorkpor</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Arena</t>
+          <t>Commonwealth 2 New</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zephaniah Lartey</t>
+          <t>David Arhin</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ATU Church</t>
+          <t>Diamond Jubilee 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>James Pekyie</t>
+          <t>Deborah Wiredu</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ATU Main Campus</t>
+          <t>Limann</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Racheal Boamah</t>
+          <t>Kwesi Boadu-Amoama</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ATU YWCA</t>
+          <t>Main Campus Dunamis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Emmanuel Otiboe</t>
+          <t>Nana Kwame Barima</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>City Campus</t>
+          <t>Main Campus Proskuneo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Abednego Abbey</t>
+          <t>Isaac Baidoo</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jamestown</t>
+          <t>Mensah Sarbah Poimen</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Joel Quartey</t>
+          <t>Prince Okai</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jamestown Allos</t>
+          <t>Prince of Peace New</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ishmael Oplerm</t>
+          <t>Joseph Akyem</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UssherFort</t>
+          <t>Revelations</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Seth Kpelebe</t>
+          <t>Edna Adorshie</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Sarbah</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Joseph Teye</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sey</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dennis Kpogli</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sey New</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Frank Anokye</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Shemen</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Samuel Agyei</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>138</v>
-      </c>
-      <c r="D11" t="n">
-        <v>329</v>
+      <c r="C15" t="n">
+        <v>27</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -15,13 +15,11 @@
     <sheet name="Colossians 5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Galatians 10" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Galatians 2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Galatians 3" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Galatians 4" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Galatians 5" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Galatians 6 A" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Galatians 7" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Galatians 8" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Galatians 9" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Galatians 4" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Galatians 5" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Galatians 6 A" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Galatians 8" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Galatians 9" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +441,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
     </row>
@@ -464,10 +462,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -482,10 +480,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>152</v>
+        <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4">
@@ -500,10 +498,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -518,10 +516,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -536,10 +534,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="D6" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -549,10 +547,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>548</v>
+        <v>203</v>
       </c>
       <c r="D7" t="n">
-        <v>203</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9">
@@ -567,10 +565,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -585,10 +583,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>329</v>
+        <v>104</v>
       </c>
       <c r="D10" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">
@@ -603,10 +601,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12">
@@ -621,10 +619,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
-        <v>88</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -639,10 +637,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>147</v>
+        <v>20</v>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -657,10 +655,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>331</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15">
@@ -670,90 +668,54 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1149</v>
+        <v>393</v>
       </c>
       <c r="D15" t="n">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Galatians 3</t>
+          <t>Galatians 6 A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Joseph Teye</t>
+          <t>Nana Kofi Danso-Mensah</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Galatians 6 A</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Jesus Night Total</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Galatians 7</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Albert Gillies Heward-Mills</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>26</v>
-      </c>
-      <c r="D19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jesus Night Total</t>
+          <t>Grand Total</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>113</v>
+        <v>625</v>
       </c>
       <c r="D20" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Grand Total</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1810</v>
-      </c>
-      <c r="D22" t="n">
-        <v>633</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>
@@ -767,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,98 +745,224 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UPSA Campus Hostels</t>
+          <t>AIT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Andrew Heward-Mills</t>
+          <t>Lawrence Adetunji</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Upsa Diaspora</t>
+          <t>AIT Yeshua</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bright Nurtey Tettey Tetteh</t>
+          <t>Jonathan Ekhagbai</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UPSA Green Hostel</t>
+          <t>Aparche</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Desmond Hlorgbey</t>
+          <t>Cyrus-Dag Stephens</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UPSA Hostels A &amp; B</t>
+          <t>Galilea</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jayson Quarshie</t>
+          <t>Lady Vanessa Osei</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>GCTU Koinonia Governorship</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Christabel Tukpeyi</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GTUC Allos</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Michael Oteng</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GTUC Allos 3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sylvester Ntumy</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GTUC Main Campus</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Jeremiah Ashong</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kings University</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Samuel Tigah</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>11</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Korle Bu Light</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sonia Elolo</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Regent University</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Prince Forson</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>152</v>
-      </c>
-      <c r="D6" t="n">
-        <v>76</v>
+      <c r="C13" t="n">
+        <v>88</v>
+      </c>
+      <c r="D13" t="n">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -888,7 +976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,60 +992,60 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AIT</t>
+          <t>Akuafo New</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lawrence Adetunji</t>
+          <t>Karyn Tagoe</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AIT Yeshua</t>
+          <t>Area 1 Royals</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jonathan Ekhagbai</t>
+          <t>Kwame Darteh</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aparche</t>
+          <t>Bani</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cyrus-Dag Stephens</t>
+          <t>Kojo Afriyie</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -970,30 +1058,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Galilea</t>
+          <t>Block A Annex</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lady Vanessa Osei</t>
+          <t>Marcia Adomako</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCTU Koinonia Governorship</t>
+          <t>Block B Annex New</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Christabel Tukpeyi</t>
+          <t>Kevin Brown</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1006,52 +1094,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GTUC Allos</t>
+          <t>Commonwealth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Michael Oteng</t>
+          <t>Peter Tefuttor</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GTUC Allos 3</t>
+          <t>Diamond Jubilee New</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sylvester Ntumy</t>
+          <t>Emelda Antwi-Agyei</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GTUC Main Campus</t>
+          <t>Evandy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jeremiah Ashong</t>
+          <t>Delali Apedu</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1060,68 +1148,140 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kings University</t>
+          <t>Evandy Annex New</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Samuel Tigah</t>
+          <t>Caroline Hammond</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Korle Bu Light</t>
+          <t>Pent B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sonia Elolo</t>
+          <t>Yves Mensah</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Regent University</t>
+          <t>Pent C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Prince Forson</t>
+          <t>Roland Cudjoe</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Pent Old &amp; A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nana Kofi Danso-Mensah</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TF Annex New</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Samuel Boateng</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Vacation Church</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Antoinette Annan</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>23</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Volta Annex New</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Esllah Osei</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>168</v>
-      </c>
-      <c r="D13" t="n">
-        <v>88</v>
+      <c r="C17" t="n">
+        <v>29</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1135,7 +1295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1151,82 +1311,82 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Akuafo New</t>
+          <t>AKUAFO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Karyn Tagoe</t>
+          <t>Foanor Alloh</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Area 1 Royals</t>
+          <t>Akuafo Zoe</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kwame Darteh</t>
+          <t>Enoch Bentil</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bani</t>
+          <t>ELU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kojo Afriyie</t>
+          <t>Tracy Osei</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Block A Annex</t>
+          <t>Legon hall</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marcia Adomako</t>
+          <t>Nana Ahema Forson</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1235,48 +1395,48 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Block B Annex New</t>
+          <t>Legon Hall B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kevin Brown</t>
+          <t>Yosi Forson</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Commonwealth</t>
+          <t>Volta</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Peter Tefuttor</t>
+          <t>Caleb Osei-Kofi</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Diamond Jubilee New</t>
+          <t>Volta Mega</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Emelda Antwi-Agyei</t>
+          <t>Doris Ainooh</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1289,158 +1449,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Evandy</t>
+          <t>Volta Others</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Delali Apedu</t>
+          <t>Rachael Sekyiwaaa</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Evandy Annex New</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Caroline Hammond</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Pent B</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Yves Mensah</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Pent C</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Roland Cudjoe</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Pent Old &amp; A</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Nana Kofi Danso-Mensah</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TF Annex New</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Samuel Boateng</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Vacation Church</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Antoinette Annan</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
         <v>23</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Volta Annex New</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Esllah Osei</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>7</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>60</v>
-      </c>
-      <c r="D17" t="n">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1454,554 +1488,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>20/09</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>27/09</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Akuafo Charis</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Stephen Asare Osei</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Akuafo Hall 1 New</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Fredrick Anokye</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Akuafo Hall 2 New</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Dacosta Amponsah</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Area 1  Logos</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Erasmus Laryea</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Commonwealth 1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Lois Osei</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Diamond Jubilee 2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Abena Kyeremaa</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Jesus Night TF New</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Jochebed Lawson-Heymann</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Kwapong</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Eunice Owusu</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Legon Hall</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Edberg Ayensu</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Main Campus Allos</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Albert Gillies Heward-Mills</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Main Campus Hagios</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Philmorra Laryea Okorley</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Main Campus Parakletos</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Melissa Meledi</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Main Campus Pistis</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Richard Mawuli Sogbo</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>10</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Main Campus Tsalach</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Jennifer Aidoo</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Main campus Zogreo</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Elinam Fiagbe</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Volta Hall</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Precious Antwi</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>26</v>
-      </c>
-      <c r="D18" t="n">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>20/09</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>27/09</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AKUAFO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Foanor Alloh</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>24</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Akuafo Hall 6</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ruby Nelson</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Akuafo Zoe</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Enoch Bentil</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>28</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ELU</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Tracy Osei</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>23</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Legon hall</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Nana Ahema Forson</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>12</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Legon Hall B</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Yosi Forson</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>17</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Volta</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Caleb Osei-Kofi</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>30</v>
-      </c>
-      <c r="D8" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Volta Mega</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Doris Ainooh</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Volta Others</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Rachael Sekyiwaaa</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>7</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>147</v>
-      </c>
-      <c r="D11" t="n">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2018,12 +1504,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
     </row>
@@ -2039,7 +1525,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
@@ -2057,10 +1543,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2075,10 +1561,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -2093,10 +1579,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -2111,7 +1597,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
@@ -2129,10 +1615,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -2147,10 +1633,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -2165,10 +1651,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -2183,10 +1669,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -2201,7 +1687,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
@@ -2219,7 +1705,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
         <v>21</v>
@@ -2232,10 +1718,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>331</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2249,7 +1735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2265,12 +1751,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
     </row>
@@ -2286,10 +1772,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2304,41 +1790,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spintex Palace</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Richard Anku</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>29</v>
-      </c>
-      <c r="D5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2352,7 +1820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2368,12 +1836,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
     </row>
@@ -2407,10 +1875,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -2425,7 +1893,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>8</v>
@@ -2443,95 +1911,77 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dome Main</t>
+          <t>Dome Ministries</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>John Amoako</t>
+          <t>Wilhermina Teprey</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dome Ministries</t>
+          <t>Dome North</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wilhermina Teprey</t>
+          <t>Pearl Addo</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dome North</t>
+          <t>Kisseman</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pearl Addo</t>
+          <t>Victoria Affran</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kisseman</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Victoria Affran</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>152</v>
-      </c>
-      <c r="D10" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2561,12 +2011,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
     </row>
@@ -2582,10 +2032,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -2600,10 +2050,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2618,10 +2068,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2636,10 +2086,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -2649,10 +2099,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2682,12 +2132,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
     </row>
@@ -2703,10 +2153,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2721,10 +2171,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -2739,7 +2189,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
@@ -2752,10 +2202,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="D5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2785,12 +2235,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2256,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -2824,10 +2274,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -2842,7 +2292,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
@@ -2860,10 +2310,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -2878,10 +2328,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -2896,10 +2346,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -2914,10 +2364,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -2927,10 +2377,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="D9" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -2944,7 +2394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2960,28 +2410,28 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ACM</t>
+          <t>ACM 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nii Nkunim Armar</t>
+          <t>Daniel Orleans-Lindsay</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -2990,16 +2440,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACM 2</t>
+          <t>ACM 3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Daniel Orleans-Lindsay</t>
+          <t>Joan Obakpolor</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -3008,32 +2458,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ACM 3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Joan Obakpolor</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>22</v>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3063,12 +2495,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
     </row>
@@ -3084,10 +2516,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -3102,10 +2534,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -3120,10 +2552,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -3138,10 +2570,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -3156,10 +2588,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -3174,10 +2606,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D7" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -3192,10 +2624,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -3210,10 +2642,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -3228,10 +2660,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -3241,10 +2673,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>329</v>
+        <v>104</v>
       </c>
       <c r="D11" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -3258,7 +2690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3274,260 +2706,80 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>20/09</t>
+          <t>27/09</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Campus Anagkazo</t>
+          <t>UPSA Campus Hostels</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nayram Gblorkpor</t>
+          <t>Andrew Heward-Mills</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Commonwealth 2 New</t>
+          <t>UPSA Green Hostel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>David Arhin</t>
+          <t>Desmond Hlorgbey</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Diamond Jubilee 1</t>
+          <t>UPSA Hostels A &amp; B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deborah Wiredu</t>
+          <t>Jayson Quarshie</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Limann</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Kwesi Boadu-Amoama</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Main Campus Dunamis</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Nana Kwame Barima</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Main Campus Proskuneo</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Isaac Baidoo</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Mensah Sarbah Poimen</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Prince Okai</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Prince of Peace New</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Joseph Akyem</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Revelations</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Edna Adorshie</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Sarbah</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Joseph Teye</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>5</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Sey</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dennis Kpogli</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sey New</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Frank Anokye</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Shemen</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Samuel Agyei</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>27</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -15,11 +15,13 @@
     <sheet name="Colossians 5" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Galatians 10" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Galatians 2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Galatians 4" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Galatians 5" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Galatians 6 A" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Galatians 8" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Galatians 9" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Galatians 3" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Galatians 4" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Galatians 5" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Galatians 6 A" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Galatians 7" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Galatians 8" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Galatians 9" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +443,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
     </row>
@@ -462,10 +464,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -480,10 +482,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="D3" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -498,7 +500,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
         <v>31</v>
@@ -516,10 +518,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -534,10 +536,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D6" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
@@ -547,10 +549,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="D7" t="n">
-        <v>219</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9">
@@ -565,10 +567,10 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
         <v>4</v>
-      </c>
-      <c r="D9" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -583,10 +585,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="D10" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11">
@@ -601,10 +603,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D11" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12">
@@ -619,10 +621,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -637,10 +639,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -655,10 +657,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D14" t="n">
-        <v>106</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15">
@@ -668,54 +670,90 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="D15" t="n">
-        <v>388</v>
+        <v>483</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Galatians 6 A</t>
+          <t>Galatians 3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Joseph Teye</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jesus Night Total</t>
+          <t>Galatians 6 A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nana Kofi Danso-Mensah</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Galatians 7</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Albert Gillies Heward-Mills</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Jesus Night Total</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>625</v>
-      </c>
-      <c r="D20" t="n">
-        <v>607</v>
+      <c r="C22" t="n">
+        <v>596</v>
+      </c>
+      <c r="D22" t="n">
+        <v>823</v>
       </c>
     </row>
   </sheetData>
@@ -729,7 +767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,224 +783,80 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AIT</t>
+          <t>UPSA Campus Hostels</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lawrence Adetunji</t>
+          <t>Andrew Heward-Mills</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AIT Yeshua</t>
+          <t>UPSA Green Hostel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Jonathan Ekhagbai</t>
+          <t>Desmond Hlorgbey</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aparche</t>
+          <t>UPSA Hostels A &amp; B</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cyrus-Dag Stephens</t>
+          <t>Jayson Quarshie</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Galilea</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Lady Vanessa Osei</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>GCTU Koinonia Governorship</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Christabel Tukpeyi</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GTUC Allos</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Michael Oteng</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>GTUC Allos 3</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Sylvester Ntumy</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GTUC Main Campus</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Jeremiah Ashong</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Kings University</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Samuel Tigah</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>11</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Korle Bu Light</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Sonia Elolo</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Regent University</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Prince Forson</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>11</v>
-      </c>
-      <c r="D12" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>88</v>
-      </c>
-      <c r="D13" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -976,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -992,64 +886,64 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Akuafo New</t>
+          <t>AIT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Karyn Tagoe</t>
+          <t>Lawrence Adetunji</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Area 1 Royals</t>
+          <t>AIT Yeshua</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kwame Darteh</t>
+          <t>Jonathan Ekhagbai</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bani</t>
+          <t>Aparche</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kojo Afriyie</t>
+          <t>Cyrus-Dag Stephens</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -1058,30 +952,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Block A Annex</t>
+          <t>Galilea</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marcia Adomako</t>
+          <t>Lady Vanessa Osei</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Block B Annex New</t>
+          <t>GCTU Koinonia Governorship</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kevin Brown</t>
+          <t>Christabel Tukpeyi</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1094,194 +988,122 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Commonwealth</t>
+          <t>GTUC Allos</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Peter Tefuttor</t>
+          <t>Michael Oteng</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Diamond Jubilee New</t>
+          <t>GTUC Allos 3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Emelda Antwi-Agyei</t>
+          <t>Sylvester Ntumy</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Evandy</t>
+          <t>GTUC Main Campus</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Delali Apedu</t>
+          <t>Jeremiah Ashong</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Evandy Annex New</t>
+          <t>Kings University</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Caroline Hammond</t>
+          <t>Samuel Tigah</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pent B</t>
+          <t>Korle Bu Light</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yves Mensah</t>
+          <t>Sonia Elolo</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pent C</t>
+          <t>Regent University</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Roland Cudjoe</t>
+          <t>Prince Forson</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pent Old &amp; A</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TF Annex New</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Samuel Boateng</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Vacation Church</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Antoinette Annan</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>23</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Volta Annex New</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Esllah Osei</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>29</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -1295,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1311,82 +1133,82 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AKUAFO</t>
+          <t>Area 1 Royals</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Foanor Alloh</t>
+          <t>Kwame Darteh</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Akuafo Zoe</t>
+          <t>Bani</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Enoch Bentil</t>
+          <t>Kojo Afriyie</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ELU</t>
+          <t>Block A Annex</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tracy Osei</t>
+          <t>Marcia Adomako</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Legon hall</t>
+          <t>Block B Annex New</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nana Ahema Forson</t>
+          <t>Kevin Brown</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1395,86 +1217,176 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Legon Hall B</t>
+          <t>Commonwealth</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Yosi Forson</t>
+          <t>Peter Tefuttor</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Volta</t>
+          <t>Diamond Jubilee New</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Caleb Osei-Kofi</t>
+          <t>Emelda Antwi-Agyei</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Volta Mega</t>
+          <t>Evandy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Doris Ainooh</t>
+          <t>Delali Apedu</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Volta Others</t>
+          <t>Pent B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rachael Sekyiwaaa</t>
+          <t>Yves Mensah</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Pent C</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Roland Cudjoe</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Pent Old &amp; A</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nana Kofi Danso-Mensah</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TF Annex New</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Samuel Boateng</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Vacation Church</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Antoinette Annan</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Volta Annex New</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Esllah Osei</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>20</v>
-      </c>
-      <c r="D10" t="n">
-        <v>23</v>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1488,7 +1400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1504,18 +1416,332 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Akuafo Charis</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Stephen Asare Osei</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Area 1  Logos</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Erasmus Laryea</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Kwapong</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Eunice Owusu</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Main Campus Parakletos</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Melissa Meledi</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Main Campus Pistis</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Richard Mawuli Sogbo</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>04/10</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>11/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AKUAFO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Foanor Alloh</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Akuafo Zoe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Enoch Bentil</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ELU</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Calebina Ikhayere</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Legon hall</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Jonathan Ephraim</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Legon Hall B</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Yosi Forson</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Volta</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Caleb Osei-Kofi</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Volta Others</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Rachael Sekyiwaaa</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>23</v>
+      </c>
+      <c r="D9" t="n">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>04/10</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>11/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>UMC Allos 1</t>
         </is>
       </c>
@@ -1528,7 +1754,7 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1543,10 +1769,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -1561,10 +1787,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -1579,10 +1805,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -1600,7 +1826,7 @@
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -1615,10 +1841,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1633,10 +1859,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -1651,10 +1877,10 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" t="n">
         <v>11</v>
-      </c>
-      <c r="D9" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1669,7 +1895,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
@@ -1690,38 +1916,20 @@
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UMC E-Church</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Divine Olubakinde</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>101</v>
-      </c>
-      <c r="D13" t="n">
-        <v>106</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1735,7 +1943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1751,12 +1959,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
     </row>
@@ -1772,10 +1980,10 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
         <v>9</v>
-      </c>
-      <c r="D2" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1790,23 +1998,41 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Spintex Palace</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Richard Anku</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>13</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C5" t="n">
         <v>18</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1836,12 +2062,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
     </row>
@@ -1875,10 +2101,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -1896,7 +2122,7 @@
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -1911,10 +2137,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -1929,10 +2155,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -1947,10 +2173,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -1965,10 +2191,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -1978,10 +2204,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="D9" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2011,12 +2237,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2258,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
@@ -2050,10 +2276,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2068,10 +2294,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -2086,7 +2312,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
@@ -2099,7 +2325,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
         <v>31</v>
@@ -2132,12 +2358,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2379,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -2171,10 +2397,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -2192,7 +2418,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -2202,10 +2428,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D5" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -2235,12 +2461,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -2274,10 +2500,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -2295,7 +2521,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -2310,10 +2536,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -2328,10 +2554,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2346,10 +2572,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -2364,10 +2590,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -2377,10 +2603,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D9" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2394,7 +2620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2410,62 +2636,44 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ACM 2</t>
+          <t>ACM 3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Daniel Orleans-Lindsay</t>
+          <t>Joan Obakpolor</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACM 3</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Joan Obakpolor</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
         <v>4</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2495,12 +2703,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
     </row>
@@ -2516,10 +2724,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2534,10 +2742,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -2552,10 +2760,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -2570,10 +2778,10 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D5" t="n">
         <v>8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -2588,7 +2796,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -2606,10 +2814,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -2624,10 +2832,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -2642,10 +2850,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -2660,10 +2868,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -2673,10 +2881,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="D11" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2690,7 +2898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2706,80 +2914,116 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>27/09</t>
+          <t>04/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>UPSA Campus Hostels</t>
+          <t>Limann</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Andrew Heward-Mills</t>
+          <t>Kwesi Boadu-Amoama</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UPSA Green Hostel</t>
+          <t>Main Campus Proskuneo</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Desmond Hlorgbey</t>
+          <t>Isaac Baidoo</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>UPSA Hostels A &amp; B</t>
+          <t>Prince of Peace New</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Jayson Quarshie</t>
+          <t>Joseph Akyem</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Sarbah</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Joseph Teye</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sey</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dennis Kpogli</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>76</v>
-      </c>
-      <c r="D5" t="n">
-        <v>75</v>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -443,12 +443,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
     </row>
@@ -464,10 +464,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
@@ -503,7 +503,7 @@
         <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="D6" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>219</v>
+        <v>276</v>
       </c>
       <c r="D7" t="n">
-        <v>276</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9">
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D10" t="n">
-        <v>129</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11">
@@ -603,10 +603,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13">
@@ -639,10 +639,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14">
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="D14" t="n">
-        <v>129</v>
+        <v>193</v>
       </c>
     </row>
     <row r="15">
@@ -670,10 +670,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>377</v>
+        <v>483</v>
       </c>
       <c r="D15" t="n">
-        <v>483</v>
+        <v>675</v>
       </c>
     </row>
     <row r="17">
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D18" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
@@ -737,10 +737,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22">
@@ -750,10 +750,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>596</v>
+        <v>823</v>
       </c>
       <c r="D22" t="n">
-        <v>823</v>
+        <v>971</v>
       </c>
     </row>
   </sheetData>
@@ -783,12 +783,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
     </row>
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -840,10 +840,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -853,10 +853,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -886,12 +886,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
     </row>
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
         <v>5</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1117,7 +1117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,60 +1133,60 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Area 1 Royals</t>
+          <t>Akuafo New</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kwame Darteh</t>
+          <t>Karyn Tagoe</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bani</t>
+          <t>Area 1 Royals</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kojo Afriyie</t>
+          <t>Kwame Darteh</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Block A Annex</t>
+          <t>Bani</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Marcia Adomako</t>
+          <t>Kojo Afriyie</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -1199,12 +1199,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Block B Annex New</t>
+          <t>Block A Annex</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kevin Brown</t>
+          <t>Marcia Adomako</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1217,12 +1217,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Commonwealth</t>
+          <t>Block B Annex New</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Peter Tefuttor</t>
+          <t>Kevin Brown</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1235,138 +1235,138 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Diamond Jubilee New</t>
+          <t>Commonwealth</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Emelda Antwi-Agyei</t>
+          <t>Peter Tefuttor</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Evandy</t>
+          <t>Diamond Jubilee New</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Delali Apedu</t>
+          <t>Emelda Antwi-Agyei</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pent B</t>
+          <t>Evandy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Yves Mensah</t>
+          <t>Delali Apedu</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pent C</t>
+          <t>Evandy Annex New</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Roland Cudjoe</t>
+          <t>Caroline Hammond</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pent Old &amp; A</t>
+          <t>Pent B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Yves Mensah</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TF Annex New</t>
+          <t>Pent C</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Samuel Boateng</t>
+          <t>Roland Cudjoe</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vacation Church</t>
+          <t>Pent Old &amp; A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Antoinette Annan</t>
+          <t>Nana Kofi Danso-Mensah</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Volta Annex New</t>
+          <t>TF Annex New</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Esllah Osei</t>
+          <t>Samuel Boateng</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1379,14 +1379,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Vacation Church</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Antoinette Annan</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Volta Annex New</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Esllah Osei</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="C17" t="n">
         <v>45</v>
+      </c>
+      <c r="D17" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1400,7 +1436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1416,12 +1452,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
     </row>
@@ -1455,10 +1491,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1482,12 +1518,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Main Campus Parakletos</t>
+          <t>Legon Hall</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Melissa Meledi</t>
+          <t>Edberg Ayensu</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1500,31 +1536,67 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Main Campus Pistis</t>
+          <t>Main Campus Allos</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Richard Mawuli Sogbo</t>
+          <t>Albert Gillies Heward-Mills</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Main Campus Parakletos</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Melissa Meledi</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Main Campus Pistis</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Richard Mawuli Sogbo</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1539,7 +1611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1555,12 +1627,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
     </row>
@@ -1576,10 +1648,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -1594,10 +1666,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -1612,10 +1684,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -1633,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1651,7 +1723,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1666,21 +1738,21 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Volta Others</t>
+          <t>Volta Mega</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rachael Sekyiwaaa</t>
+          <t>Doris Ainooh</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1693,14 +1765,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Volta Others</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Rachael Sekyiwaaa</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>23</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="C10" t="n">
         <v>36</v>
+      </c>
+      <c r="D10" t="n">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1730,12 +1820,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
     </row>
@@ -1751,10 +1841,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1769,10 +1859,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -1787,10 +1877,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -1805,10 +1895,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -1823,10 +1913,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -1841,10 +1931,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1859,10 +1949,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -1877,10 +1967,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -1898,7 +1988,7 @@
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -1913,10 +2003,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -1926,10 +2016,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -1959,12 +2049,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
     </row>
@@ -1980,10 +2070,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -1998,7 +2088,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
@@ -2029,10 +2119,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -2062,12 +2152,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
     </row>
@@ -2101,10 +2191,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -2119,10 +2209,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -2137,7 +2227,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
         <v>16</v>
@@ -2155,10 +2245,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -2173,10 +2263,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -2191,10 +2281,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -2204,10 +2294,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2237,12 +2327,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2351,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2276,10 +2366,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2294,7 +2384,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D4" t="n">
         <v>17</v>
@@ -2315,7 +2405,7 @@
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2328,7 +2418,7 @@
         <v>31</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -2358,12 +2448,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2397,10 +2487,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -2415,10 +2505,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -2428,10 +2518,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2461,12 +2551,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
     </row>
@@ -2482,10 +2572,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2500,10 +2590,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -2518,10 +2608,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -2536,10 +2626,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -2554,10 +2644,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -2572,10 +2662,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -2590,10 +2680,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -2603,10 +2693,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="D9" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2636,12 +2726,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
     </row>
@@ -2657,10 +2747,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2670,10 +2760,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2703,12 +2793,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
     </row>
@@ -2724,10 +2814,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2742,10 +2832,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -2760,10 +2850,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -2778,10 +2868,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -2799,7 +2889,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -2814,10 +2904,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -2832,10 +2922,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -2850,10 +2940,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -2868,10 +2958,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
@@ -2881,10 +2971,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -2914,12 +3004,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>04/10</t>
+          <t>11/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
     </row>
@@ -2956,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2989,10 +3079,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3007,7 +3097,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
@@ -3020,10 +3110,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Sunday_Arrivals.xlsx
+++ b/Sunday_Arrivals.xlsx
@@ -22,6 +22,7 @@
     <sheet name="Galatians 7" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Galatians 8" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Galatians 9" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Jesus Night Town Church" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -443,12 +444,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>18/10</t>
+          <t>25/10</t>
         </is>
       </c>
     </row>
@@ -464,10 +465,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -482,10 +483,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D3" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
@@ -500,10 +501,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -518,10 +519,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -536,10 +537,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D6" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -549,10 +550,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>276</v>
+        <v>245</v>
       </c>
       <c r="D7" t="n">
-        <v>245</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9">
@@ -567,10 +568,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -585,10 +586,10 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>196</v>
+      </c>
+      <c r="D10" t="n">
         <v>129</v>
-      </c>
-      <c r="D10" t="n">
-        <v>196</v>
       </c>
     </row>
     <row r="11">
@@ -603,10 +604,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -621,10 +622,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>114</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -639,10 +640,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>67</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -657,10 +658,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>129</v>
+        <v>193</v>
       </c>
       <c r="D14" t="n">
-        <v>193</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15">
@@ -670,10 +671,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>483</v>
+        <v>675</v>
       </c>
       <c r="D15" t="n">
-        <v>675</v>
+        <v>460</v>
       </c>
     </row>
     <row r="17">
@@ -688,10 +689,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
@@ -706,10 +707,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19">
@@ -724,36 +725,54 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Jesus Night Town Church</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Joseph Teye</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Jesus Night Total</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>64</v>
-      </c>
-      <c r="D20" t="n">
+      <c r="C21" t="n">
         <v>51</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="D21" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>823</v>
-      </c>
-      <c r="D22" t="n">
+      <c r="C23" t="n">
         <v>971</v>
+      </c>
+      <c r="D23" t="n">
+        <v>882</v>
       </c>
     </row>
   </sheetData>
@@ -783,12 +802,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>18/10</t>
+          <t>25/10</t>
         </is>
       </c>
     </row>
@@ -804,10 +823,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
@@ -822,7 +841,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
         <v>16</v>
@@ -840,10 +859,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -853,10 +872,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D5" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -886,12 +905,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>18/10</t>
+          <t>25/10</t>
         </is>
       </c>
     </row>
@@ -907,7 +926,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
@@ -925,10 +944,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -943,10 +962,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -961,10 +980,10 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>32</v>
+      </c>
+      <c r="D5" t="n">
         <v>25</v>
-      </c>
-      <c r="D5" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -997,10 +1016,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -1015,10 +1034,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1033,10 +1052,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1051,10 +1070,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1069,10 +1088,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -1090,7 +1109,7 @@
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -1100,10 +1119,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
-        <v>114</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1117,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,12 +1152,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>18/10</t>
+          <t>25/10</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1172,10 +1191,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -1193,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -1211,7 +1230,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -1229,40 +1248,40 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Commonwealth</t>
+          <t>Diamond Jubilee New</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Peter Tefuttor</t>
+          <t>Emelda Antwi-Agyei</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Diamond Jubilee New</t>
+          <t>Evandy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Emelda Antwi-Agyei</t>
+          <t>Kojo Afriyie</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -1271,158 +1290,140 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Evandy</t>
+          <t>Evandy Annex New</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Delali Apedu</t>
+          <t>Caroline Hammond</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Evandy Annex New</t>
+          <t>Pent Old &amp; A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Caroline Hammond</t>
+          <t>Nana Kofi Danso-Mensah</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pent B</t>
+          <t>TF Annex New</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Yves Mensah</t>
+          <t>Samuel Boateng</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pent C</t>
+          <t>Upsa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Roland Cudjoe</t>
+          <t>Delali Apedu</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Pent Old &amp; A</t>
+          <t>Vacation Church</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nana Kofi Danso-Mensah</t>
+          <t>Antoinette Annan</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TF Annex New</t>
+          <t>Volta Annex New</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Samuel Boateng</t>
+          <t>Esllah Osei</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Vacation Church</t>
+          <t>Wisconsin</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Antoinette Annan</t>
+          <t>Roland Cudjoe</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Volta Annex New</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Esllah Osei</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>45</v>
-      </c>
-      <c r="D17" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -1436,7 +1437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1452,12 +1453,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>18/10</t>
+          <t>25/10</t>
         </is>
       </c>
     </row>
@@ -1476,25 +1477,25 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Area 1  Logos</t>
+          <t>Akuafo Hall 1 New</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Erasmus Laryea</t>
+          <t>Fredrick Anokye</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1530,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1548,18 +1549,18 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Main Campus Parakletos</t>
+          <t>Main Campus Hagios</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Melissa Meledi</t>
+          <t>Philmorra Laryea Okorley</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1572,32 +1573,104 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Main Campus Pistis</t>
+          <t>Main Campus Parakletos</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Richard Mawuli Sogbo</t>
+          <t>Melissa Meledi</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Main Campus Pistis</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Clement Appoh</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Main Campus Tsalach</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Jennifer Aidoo</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Main campus Zogreo</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Elinam Fiagbe</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Volta Hall</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Precious Antwi</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>7</v>
-      </c>
-      <c r="D9" t="n">
-        <v>7</v>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1627,12 +1700,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>18/10</t>
+          <t>25/10</t>
         </is>
       </c>
     </row>
@@ -1648,10 +1721,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1666,10 +1739,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -1684,10 +1757,10 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" t="n">
         <v>3</v>
-      </c>
-      <c r="D4" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -1702,10 +1775,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1720,10 +1793,10 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
         <v>2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1738,10 +1811,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -1774,10 +1847,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1787,10 +1860,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="D10" t="n">
-        <v>67</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1820,12 +1893,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>18/10</t>
+          <t>25/10</t>
         </is>
       </c>
     </row>
@@ -1841,10 +1914,10 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>27</v>
+      </c>
+      <c r="D2" t="n">
         <v>10</v>
-      </c>
-      <c r="D2" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1859,10 +1932,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1877,10 +1950,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -1895,10 +1968,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -1913,10 +1986,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -1931,10 +2004,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1949,10 +2022,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -1967,10 +2040,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -1985,10 +2058,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -2003,10 +2076,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D11" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -2016,10 +2089,167 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>193</v>
       </c>
       <c r="D12" t="n">
-        <v>193</v>
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>18/10</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>25/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Adjiriganor</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Yves Mensah</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Haatso</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dennis Kpogli</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Madina Estate</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Joseph Teye</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Madina Rawlings circle</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Richard Mawuli Sogbo</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mempeasem</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Peter Tefuttor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ogbojo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Erasmus Laryea</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2033,7 +2263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2049,12 +2279,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>18/10</t>
+          <t>25/10</t>
         </is>
       </c>
     </row>
@@ -2070,10 +2300,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2091,38 +2321,20 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spintex Palace</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Richard Anku</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -2152,12 +2364,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>18/10</t>
+          <t>25/10</t>
         </is>
       </c>
     </row>
@@ -2191,10 +2403,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2209,10 +2421,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -2245,10 +2457,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -2263,10 +2475,10 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" t="n">
         <v>15</v>
-      </c>
-      <c r="D7" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -2281,10 +2493,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -2294,10 +2506,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D9" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2327,12 +2539,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>18/10</t>
+          <t>25/10</t>
         </is>
       </c>
     </row>
@@ -2348,10 +2560,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -2366,10 +2578,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2387,7 +2599,7 @@
         <v>17</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -2402,10 +2614,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2415,10 +2627,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2448,12 +2660,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>18/10</t>
+          <t>25/10</t>
         </is>
       </c>
     </row>
@@ -2469,10 +2681,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -2487,10 +2699,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -2505,10 +2717,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -2518,10 +2730,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2551,12 +2763,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>18/10</t>
+          <t>25/10</t>
         </is>
       </c>
     </row>
@@ -2572,10 +2784,10 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>4</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2590,10 +2802,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -2608,10 +2820,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -2626,10 +2838,10 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>9</v>
+      </c>
+      <c r="D5" t="n">
         <v>12</v>
-      </c>
-      <c r="D5" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -2644,10 +2856,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -2662,10 +2874,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -2680,10 +2892,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -2693,10 +2905,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2710,7 +2922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2726,44 +2938,62 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>18/10</t>
+          <t>25/10</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ACM 3</t>
+          <t>ACM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Joan Obakpolor</t>
+          <t>Nii Nkunim Armar</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>ACM 3</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Joan Obakpolor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C4" t="n">
         <v>12</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2793,12 +3023,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>18/10</t>
+          <t>25/10</t>
         </is>
       </c>
     </row>
@@ -2814,10 +3044,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2832,10 +3062,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -2850,10 +3080,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -2868,10 +3098,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -2886,10 +3116,10 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
         <v>8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -2904,10 +3134,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D7" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -2922,10 +3152,10 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>36</v>
+      </c>
+      <c r="D8" t="n">
         <v>10</v>
-      </c>
-      <c r="D8" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -2940,10 +3170,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -2958,10 +3188,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D10" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2971,10 +3201,10 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>196</v>
+      </c>
+      <c r="D11" t="n">
         <v>129</v>
-      </c>
-      <c r="D11" t="n">
-        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -2988,7 +3218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3004,12 +3234,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>11/10</t>
+          <t>18/10</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>18/10</t>
+          <t>25/10</t>
         </is>
       </c>
     </row>
@@ -3028,40 +3258,40 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Main Campus Proskuneo</t>
+          <t>Main Campus Dunamis</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Isaac Baidoo</t>
+          <t>Nana Kwame Barima</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Prince of Peace New</t>
+          <t>Main Campus Proskuneo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Joseph Akyem</t>
+          <t>Isaac Baidoo</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -3070,50 +3300,86 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sarbah</t>
+          <t>Mensah Sarbah Poimen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Joseph Teye</t>
+          <t>Prince Okai</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sey</t>
+          <t>Prince of Peace New</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dennis Kpogli</t>
+          <t>Joseph Akyem</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Sey</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Edna Avuletey</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sey New</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Frank Anokye</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>12</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="C9" t="n">
         <v>5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
